--- a/data/trans_orig/Q5408-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5408-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el bater en 2007</t>
+          <t>Población según si es capaz de usar el bater en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>25475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20341</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42604</t>
+          <t>44225</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36730</t>
+          <t>36020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63286</t>
+          <t>64140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>345551</t>
+          <t>345629</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>361407</t>
+          <t>361523</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>540607</t>
+          <t>538262</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>564073</t>
+          <t>562767</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>890813</t>
+          <t>889449</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>919298</t>
+          <t>919868</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5762</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5663</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6655</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6801</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83994</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55108</t>
+          <t>54942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141928</t>
+          <t>141898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149496</t>
+          <t>149471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1758,97 +1758,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>10443</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25619</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45873</t>
+          <t>46508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36771</t>
+          <t>36346</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64134</t>
+          <t>63735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474333</t>
+          <t>474144</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>490015</t>
+          <t>490459</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>625105</t>
+          <t>624222</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>651198</t>
+          <t>650411</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1107353</t>
+          <t>1107294</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1136569</t>
+          <t>1136691</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el bater en 2012</t>
+          <t>Población según si es capaz de usar el bater en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19414</t>
+          <t>20499</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9673</t>
+          <t>9668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27666</t>
+          <t>27247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39655</t>
+          <t>39260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>14529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34529</t>
+          <t>33987</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28991</t>
+          <t>30261</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55695</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48949</t>
+          <t>49096</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81913</t>
+          <t>81277</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>368810</t>
+          <t>367750</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>391816</t>
+          <t>392739</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>560604</t>
+          <t>558211</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>590405</t>
+          <t>589771</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>938470</t>
+          <t>938004</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>976822</t>
+          <t>975805</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110426</t>
+          <t>109598</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117661</t>
+          <t>117674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73612</t>
+          <t>73950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82050</t>
+          <t>82118</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187905</t>
+          <t>187887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199398</t>
+          <t>199286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -3700,97 +3700,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42721</t>
+          <t>42215</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30112</t>
+          <t>28842</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18621</t>
+          <t>18769</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43354</t>
+          <t>42316</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38257</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>32375</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59040</t>
+          <t>59022</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55482</t>
+          <t>54938</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88084</t>
+          <t>89159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>509032</t>
+          <t>509512</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>533280</t>
+          <t>533224</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660508</t>
+          <t>660911</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>691131</t>
+          <t>691306</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1180018</t>
+          <t>1180844</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1219568</t>
+          <t>1220172</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el bater en 2016</t>
+          <t>Población según si es capaz de usar el bater en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30044</t>
+          <t>30881</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28384</t>
+          <t>28736</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>19300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44072</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36832</t>
+          <t>37485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65740</t>
+          <t>66207</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>319836</t>
+          <t>319694</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>337466</t>
+          <t>337056</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>496284</t>
+          <t>495444</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>524145</t>
+          <t>524723</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>820877</t>
+          <t>822632</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>855916</t>
+          <t>856549</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2283</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4459</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4529</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>183939</t>
+          <t>183341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>178987</t>
+          <t>177796</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>187068</t>
+          <t>187070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>366372</t>
+          <t>365836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>377644</t>
+          <t>377504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -5755,97 +5755,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>37671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67356</t>
+          <t>67887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>2436</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23349</t>
+          <t>23397</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30089</t>
+          <t>30717</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33652</t>
+          <t>33347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23616</t>
+          <t>23660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48930</t>
+          <t>49921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43628</t>
+          <t>45103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74184</t>
+          <t>75116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>548736</t>
+          <t>548513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>568632</t>
+          <t>568020</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>712138</t>
+          <t>712496</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>741594</t>
+          <t>741472</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1270286</t>
+          <t>1269293</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1303647</t>
+          <t>1303671</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el bater en 2023</t>
+          <t>Población según si es capaz de usar el bater en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>12665</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24595</t>
+          <t>24865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19282</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37465</t>
+          <t>37362</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56118</t>
+          <t>55909</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48330</t>
+          <t>49592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70118</t>
+          <t>71846</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>246576</t>
+          <t>246395</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>258608</t>
+          <t>258194</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>427886</t>
+          <t>428355</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>449225</t>
+          <t>449898</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>680057</t>
+          <t>680330</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>704637</t>
+          <t>704389</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19773</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25216</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>258626</t>
+          <t>258813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268222</t>
+          <t>268246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>432246</t>
+          <t>433260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>452292</t>
+          <t>452671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>699013</t>
+          <t>698312</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>720738</t>
+          <t>720825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>816</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7845,62 +7845,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -7923,97 +7923,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2134</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>381</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1917</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1915</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104169</t>
+          <t>104170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69408</t>
+          <t>69191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>174074</t>
+          <t>174167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23500</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12972</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30333</t>
+          <t>29559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>13512</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28583</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29320</t>
+          <t>28633</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73902</t>
+          <t>74298</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,42 +8429,42 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>75368</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>47741</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>93054</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>2,85%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>75368</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>49002</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>93048</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>612503</t>
+          <t>614004</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>628660</t>
+          <t>629639</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>932796</t>
+          <t>931932</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>989430</t>
+          <t>991031</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1557563</t>
+          <t>1557884</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1613181</t>
+          <t>1613204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">

--- a/data/trans_orig/Q5408-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5408-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>12896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25475</t>
+          <t>25255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20514</t>
+          <t>20949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44225</t>
+          <t>43333</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36020</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64140</t>
+          <t>63917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>361523</t>
+          <t>362122</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>538262</t>
+          <t>539585</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>562767</t>
+          <t>563044</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>889449</t>
+          <t>889954</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>919868</t>
+          <t>920341</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,77 +1322,77 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5266</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>7187</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>4578</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5650</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>83918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54942</t>
+          <t>55259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141898</t>
+          <t>141236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149471</t>
+          <t>149481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25780</t>
+          <t>26246</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46508</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36346</t>
+          <t>34743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63735</t>
+          <t>63138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474144</t>
+          <t>474315</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>490459</t>
+          <t>489966</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>624222</t>
+          <t>625202</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>650411</t>
+          <t>649307</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1107294</t>
+          <t>1108311</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1136691</t>
+          <t>1137175</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20499</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>27574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39260</t>
+          <t>41251</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14529</t>
+          <t>15007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33987</t>
+          <t>33807</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30261</t>
+          <t>29456</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57907</t>
+          <t>54439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49096</t>
+          <t>48692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81277</t>
+          <t>81695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>367750</t>
+          <t>368637</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>392739</t>
+          <t>391488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>558211</t>
+          <t>560758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>589771</t>
+          <t>590820</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>938004</t>
+          <t>938261</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>975805</t>
+          <t>976152</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109598</t>
+          <t>110307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117674</t>
+          <t>117698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73950</t>
+          <t>73758</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82118</t>
+          <t>82086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187887</t>
+          <t>187992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199286</t>
+          <t>199284</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42215</t>
+          <t>42194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>19239</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28842</t>
+          <t>29189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18769</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42316</t>
+          <t>42684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32375</t>
+          <t>32423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59022</t>
+          <t>59310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54938</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>89159</t>
+          <t>88808</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>509512</t>
+          <t>509255</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>533224</t>
+          <t>532930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660911</t>
+          <t>659656</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>691306</t>
+          <t>691621</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1180844</t>
+          <t>1180305</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1220172</t>
+          <t>1219939</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>24225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30881</t>
+          <t>29813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28736</t>
+          <t>28784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>44190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37485</t>
+          <t>37667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66207</t>
+          <t>67694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>319694</t>
+          <t>319985</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>337056</t>
+          <t>337202</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>495444</t>
+          <t>495642</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>524723</t>
+          <t>523992</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>822632</t>
+          <t>822973</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>856549</t>
+          <t>855047</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>13538</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>183341</t>
+          <t>183867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191614</t>
+          <t>191540</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177796</t>
+          <t>178260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>187070</t>
+          <t>187073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>365836</t>
+          <t>365842</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>377504</t>
+          <t>377469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>37576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67887</t>
+          <t>67683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23397</t>
+          <t>23798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30717</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33347</t>
+          <t>33315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23660</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49921</t>
+          <t>49490</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45103</t>
+          <t>44853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75116</t>
+          <t>75981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>548513</t>
+          <t>549423</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>568020</t>
+          <t>568255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>712496</t>
+          <t>710863</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>741472</t>
+          <t>740455</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1269293</t>
+          <t>1268934</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1303671</t>
+          <t>1304637</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21319</t>
+          <t>23193</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>19322</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>13496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24865</t>
+          <t>27050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>13199</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18720</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46194</t>
+          <t>48745</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37362</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55909</t>
+          <t>60429</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>58860</t>
+          <t>61944</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49592</t>
+          <t>51695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71846</t>
+          <t>75148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>253385</t>
+          <t>273569</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>246395</t>
+          <t>266650</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>258194</t>
+          <t>278659</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>439471</t>
+          <t>473352</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>428355</t>
+          <t>459708</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>449898</t>
+          <t>484353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>692856</t>
+          <t>746922</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>680330</t>
+          <t>733211</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>704389</t>
+          <t>759395</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>500154</t>
+          <t>538092</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>500154</t>
+          <t>538092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>500154</t>
+          <t>538092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>769398</t>
+          <t>828188</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>769398</t>
+          <t>828188</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>769398</t>
+          <t>828188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,27 +7424,27 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7687</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>10042</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>264366</t>
+          <t>294803</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>258813</t>
+          <t>288516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268246</t>
+          <t>298525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>444885</t>
+          <t>265893</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>433260</t>
+          <t>260561</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>452671</t>
+          <t>269901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>709251</t>
+          <t>560695</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>698312</t>
+          <t>553065</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>720825</t>
+          <t>566592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>397</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>397</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -7998,12 +7998,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -8031,27 +8031,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>104828</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104170</t>
+          <t>114899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8066,27 +8066,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>70944</t>
+          <t>82458</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69191</t>
+          <t>80694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8101,27 +8101,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>175772</t>
+          <t>200681</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>174167</t>
+          <t>197988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,22 +8261,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>17707</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23100</t>
+          <t>24675</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>16837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>32177</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19580</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27533</t>
+          <t>28477</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>55788</t>
+          <t>59184</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28633</t>
+          <t>49311</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74298</t>
+          <t>71569</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>75368</t>
+          <t>79498</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47741</t>
+          <t>67836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>93054</t>
+          <t>95005</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>622578</t>
+          <t>686594</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>614004</t>
+          <t>677648</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>629639</t>
+          <t>694118</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>955300</t>
+          <t>821703</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>931932</t>
+          <t>807066</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>991031</t>
+          <t>832790</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1577877</t>
+          <t>1508298</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1557884</t>
+          <t>1490842</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1613204</t>
+          <t>1521503</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1027218</t>
+          <t>898593</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1027218</t>
+          <t>898593</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1027218</t>
+          <t>898593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1674704</t>
+          <t>1611395</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1674704</t>
+          <t>1611395</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1674704</t>
+          <t>1611395</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
